--- a/order_forms/029_titleist--order_forms.xlsx
+++ b/order_forms/029_titleist--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="43" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -750,7 +750,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>date_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>note_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_one_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_multiple_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>date_3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Date 3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>note_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Additional Information</t>
+          <t>Note 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,7 +934,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_one_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_multiple_3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Which services would you like to add?</t>
+          <t>Select Multiple 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 3</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>phone_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>date_4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Date 4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>note_4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Additional Information</t>
+          <t>Note 4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>note_5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1101,7 +1101,7 @@
   <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="27" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1279,7 +1279,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1296,7 +1296,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1313,7 +1313,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1330,7 +1330,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,7 +1347,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1364,7 +1364,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1381,7 +1381,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_3_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1398,7 +1398,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_3_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1415,7 +1415,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_3_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1432,7 +1432,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple_3_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1449,7 +1449,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple_3_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1466,7 +1466,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple_3_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
